--- a/test/FIWDEE_IntegrationTest_Design.xlsx
+++ b/test/FIWDEE_IntegrationTest_Design.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\ProjectPOS\FIWDEE-CP353002-69_1PrinciplesOfSoftwareDesign\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C54B3046-2E6E-4D69-AE1E-F13D05A5D2F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAC00310-1326-44E8-90F7-B7BFCEB8B029}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Summary" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1875" uniqueCount="912">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1886" uniqueCount="908">
   <si>
     <t>FIWDEE – Integration Test Design (backend + PostgreSQL, เวอร์ชัน develop ล่าสุด)</t>
   </si>
@@ -2659,12 +2659,6 @@
     <t>Lenovo LOQ 15AHP11, CPU AMD Ryzen 7 250, Memory 16 GB DDR5, GPU NVIDIA GeForce RTX 5050 Laptop, OS Window 11</t>
   </si>
   <si>
-    <t>DEF-013, DEF-014, DEF-017</t>
-  </si>
-  <si>
-    <t>DEF-016, DEF-018</t>
-  </si>
-  <si>
     <t>ได้ข้อความ "CONFIRMED"</t>
   </si>
   <si>
@@ -2740,9 +2734,6 @@
     <t>(I6) 403</t>
   </si>
   <si>
-    <t>transaction rollback</t>
-  </si>
-  <si>
     <t xml:space="preserve">(I4) มี payment สถานะ FAILED 1 แถวเป็นหลักฐาน </t>
   </si>
   <si>
@@ -2752,21 +2743,12 @@
     <t>Q002</t>
   </si>
   <si>
-    <t>จองซ้อน</t>
-  </si>
-  <si>
     <t>ทุกรอบสำเร็จ 1 request (201) ที่เหลือ 409 • ฐานข้อมูลมี booking รอบละ 1 แถว</t>
   </si>
   <si>
-    <t>คิวค้าง IN_SERVICE ห้องค้าง OCCUPIED และหมอนวดกด complete ไม่ได้</t>
-  </si>
-  <si>
     <t xml:space="preserve">booking COMPLETED และคิว COMPLETED, ห้อง CLEANING (Scenario 3 Phase D) </t>
   </si>
   <si>
-    <t>เป็น COMPLETED ทั้งที่ยังไม่จ่าย</t>
-  </si>
-  <si>
     <t>booking ยัง IN_SERVICE รอชำระ</t>
   </si>
   <si>
@@ -2783,6 +2765,12 @@
   </si>
   <si>
     <t>service/impl/PaymentServiceImpl save payment FAILED แล้ว throw ValidationException ใน @Transactional เดียวกัน จึงถูก rollback • Unit test (verify save FAILED) ผ่านเพราะใช้ mock แต่ของจริงไม่บันทึก • UC-19b • IT09-TC012</t>
+  </si>
+  <si>
+    <t>มี payment สถานะ FAILED 1 แถวเป็นหลักฐาน</t>
+  </si>
+  <si>
+    <t>booking COMPLETED และคิว COMPLETED, ห้อง CLEANING</t>
   </si>
 </sst>
 </file>
@@ -2975,10 +2963,12 @@
     <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2994,6 +2984,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3004,14 +2998,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3020,12 +3014,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3793,11 +3781,11 @@
       </c>
       <c r="E8" s="3">
         <f>COUNTIF(IT04_RoleAccess_DT!$G$27:$G$76,"Pass")</f>
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F8" s="3">
         <f>COUNTIF(IT04_RoleAccess_DT!$G$27:$G$76,"Fail")</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G8" s="3">
         <f>COUNTIF(IT04_RoleAccess_DT!$G$27:$G$76,"No run")</f>
@@ -3807,9 +3795,7 @@
         <f>COUNTIF(IT04_RoleAccess_DT!$G$27:$G$76,"Block")</f>
         <v>0</v>
       </c>
-      <c r="I8" s="4" t="s">
-        <v>19</v>
-      </c>
+      <c r="I8" s="4"/>
     </row>
     <row r="9" spans="1:9" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
@@ -3827,11 +3813,11 @@
       </c>
       <c r="E9" s="3">
         <f>COUNTIF(IT05_ErrorContract_EC!$F$24:$F$33,"Pass")</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F9" s="3">
         <f>COUNTIF(IT05_ErrorContract_EC!$F$24:$F$33,"Fail")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G9" s="3">
         <f>COUNTIF(IT05_ErrorContract_EC!$F$24:$F$33,"No run")</f>
@@ -3841,9 +3827,7 @@
         <f>COUNTIF(IT05_ErrorContract_EC!$F$24:$F$33,"Block")</f>
         <v>0</v>
       </c>
-      <c r="I9" s="4" t="s">
-        <v>21</v>
-      </c>
+      <c r="I9" s="4"/>
     </row>
     <row r="10" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="26" t="s">
@@ -3970,11 +3954,11 @@
       </c>
       <c r="E14" s="3">
         <f>COUNTIF(IT09_PaymentRefundApi_EC!$F$21:$F$35,"Pass")</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F14" s="3">
         <f>COUNTIF(IT09_PaymentRefundApi_EC!$F$21:$F$35,"Fail")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G14" s="3">
         <f>COUNTIF(IT09_PaymentRefundApi_EC!$F$21:$F$35,"No run")</f>
@@ -3984,9 +3968,7 @@
         <f>COUNTIF(IT09_PaymentRefundApi_EC!$F$21:$F$35,"Block")</f>
         <v>0</v>
       </c>
-      <c r="I14" s="4" t="s">
-        <v>871</v>
-      </c>
+      <c r="I14" s="4"/>
     </row>
     <row r="15" spans="1:9" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
@@ -4049,11 +4031,11 @@
       </c>
       <c r="E17" s="3">
         <f>COUNTIF(IT11_EndToEndFlow_SC!$F$20:$F$27,"Pass")</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F17" s="3">
         <f>COUNTIF(IT11_EndToEndFlow_SC!$F$20:$F$27,"Fail")</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G17" s="3">
         <f>COUNTIF(IT11_EndToEndFlow_SC!$F$20:$F$27,"No run")</f>
@@ -4063,9 +4045,7 @@
         <f>COUNTIF(IT11_EndToEndFlow_SC!$F$20:$F$27,"Block")</f>
         <v>0</v>
       </c>
-      <c r="I17" s="4" t="s">
-        <v>870</v>
-      </c>
+      <c r="I17" s="4"/>
     </row>
     <row r="18" spans="1:9" ht="86.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
@@ -4083,11 +4063,11 @@
       </c>
       <c r="E18" s="3">
         <f>COUNTIF(IT12_AdminConfigImpact_EC!$F$19:$F$26,"Pass")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F18" s="3">
         <f>COUNTIF(IT12_AdminConfigImpact_EC!$F$19:$F$26,"Fail")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" s="3">
         <f>COUNTIF(IT12_AdminConfigImpact_EC!$F$19:$F$26,"No run")</f>
@@ -4097,9 +4077,7 @@
         <f>COUNTIF(IT12_AdminConfigImpact_EC!$F$19:$F$26,"Block")</f>
         <v>0</v>
       </c>
-      <c r="I18" s="4" t="s">
-        <v>19</v>
-      </c>
+      <c r="I18" s="4"/>
     </row>
     <row r="19" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A19" s="24" t="s">
@@ -4113,11 +4091,11 @@
       </c>
       <c r="E19" s="6">
         <f>SUMPRODUCT(ISNUMBER(E3:E18)*E3:E18)</f>
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="F19" s="7">
         <f>SUMPRODUCT(ISNUMBER(F3:F18)*F3:F18)</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G19" s="5">
         <f>SUMPRODUCT(ISNUMBER(G3:G18)*G3:G18)</f>
@@ -4199,14 +4177,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="33" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
       <c r="I1" s="4"/>
       <c r="J1" s="5" t="s">
         <v>543</v>
@@ -4236,11 +4214,11 @@
       <c r="A3" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="34" t="s">
         <v>549</v>
       </c>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
       <c r="E3" s="9" t="s">
         <v>102</v>
       </c>
@@ -4264,11 +4242,11 @@
       <c r="A4" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="34" t="s">
         <v>553</v>
       </c>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
       <c r="E4" s="9" t="s">
         <v>110</v>
       </c>
@@ -4292,15 +4270,15 @@
       <c r="A5" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="34" t="s">
         <v>869</v>
       </c>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="32"/>
       <c r="E5" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="F5" s="41">
+      <c r="F5" s="20">
         <v>46305</v>
       </c>
     </row>
@@ -4308,55 +4286,55 @@
       <c r="A6" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="30"/>
-      <c r="D6" s="30"/>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="32"/>
     </row>
     <row r="7" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="34" t="s">
         <v>558</v>
       </c>
-      <c r="C7" s="30"/>
-      <c r="D7" s="30"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
+      <c r="C7" s="32"/>
+      <c r="D7" s="32"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="32"/>
     </row>
     <row r="9" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="29" t="s">
+      <c r="A9" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="C9" s="30"/>
-      <c r="D9" s="29" t="s">
+      <c r="C9" s="32"/>
+      <c r="D9" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="E9" s="29" t="s">
+      <c r="E9" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="F9" s="29" t="s">
+      <c r="F9" s="31" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="30"/>
+      <c r="A10" s="32"/>
       <c r="B10" s="5" t="s">
         <v>559</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="D10" s="30"/>
-      <c r="E10" s="30"/>
-      <c r="F10" s="30"/>
+      <c r="D10" s="32"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="32"/>
     </row>
     <row r="11" spans="1:12" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
@@ -4780,26 +4758,26 @@
       <c r="F11" s="3"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="31" t="s">
+      <c r="A13" s="33" t="s">
         <v>90</v>
       </c>
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
+      <c r="B13" s="30"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="30"/>
     </row>
     <row r="15" spans="1:7" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B15" s="32" t="s">
+      <c r="B15" s="34" t="s">
         <v>599</v>
       </c>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
       <c r="F15" s="9" t="s">
         <v>102</v>
       </c>
@@ -4811,12 +4789,12 @@
       <c r="A16" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="B16" s="32" t="s">
+      <c r="B16" s="34" t="s">
         <v>485</v>
       </c>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="32"/>
       <c r="F16" s="9" t="s">
         <v>110</v>
       </c>
@@ -4828,16 +4806,16 @@
       <c r="A17" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="B17" s="32" t="s">
+      <c r="B17" s="34" t="s">
         <v>869</v>
       </c>
-      <c r="C17" s="30"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="30"/>
+      <c r="C17" s="32"/>
+      <c r="D17" s="32"/>
+      <c r="E17" s="32"/>
       <c r="F17" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="G17" s="41">
+      <c r="G17" s="20">
         <v>46305</v>
       </c>
     </row>
@@ -4845,61 +4823,61 @@
       <c r="A18" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="B18" s="32" t="s">
+      <c r="B18" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="30"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="30"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="32"/>
+      <c r="G18" s="32"/>
     </row>
     <row r="19" spans="1:7" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="B19" s="32" t="s">
+      <c r="B19" s="34" t="s">
         <v>600</v>
       </c>
-      <c r="C19" s="30"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="30"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="32"/>
     </row>
     <row r="21" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="29" t="s">
+      <c r="A21" s="31" t="s">
         <v>354</v>
       </c>
-      <c r="B21" s="29" t="s">
+      <c r="B21" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="C21" s="29" t="s">
+      <c r="C21" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="D21" s="30"/>
-      <c r="E21" s="29" t="s">
+      <c r="D21" s="32"/>
+      <c r="E21" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="F21" s="29" t="s">
+      <c r="F21" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="G21" s="29" t="s">
+      <c r="G21" s="31" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="30"/>
-      <c r="B22" s="30"/>
+      <c r="A22" s="32"/>
+      <c r="B22" s="32"/>
       <c r="C22" s="5" t="s">
         <v>601</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>602</v>
       </c>
-      <c r="E22" s="30"/>
-      <c r="F22" s="30"/>
-      <c r="G22" s="30"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="32"/>
+      <c r="G22" s="32"/>
     </row>
     <row r="23" spans="1:7" ht="86.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
@@ -5076,7 +5054,7 @@
         <v>440</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="F30" s="4">
         <v>200</v>
@@ -5138,44 +5116,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="37" t="s">
         <v>183</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
     </row>
     <row r="2" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="E2" s="37" t="s">
+      <c r="E2" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="F2" s="38"/>
+      <c r="F2" s="40"/>
     </row>
     <row r="3" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="B3" s="39" t="s">
+      <c r="B3" s="41" t="s">
         <v>187</v>
       </c>
-      <c r="C3" s="40"/>
+      <c r="C3" s="42"/>
       <c r="E3" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="F3" s="39" t="s">
+      <c r="F3" s="41" t="s">
         <v>187</v>
       </c>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
     </row>
     <row r="4" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
@@ -5286,27 +5264,27 @@
       <c r="I9" s="36"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="31" t="s">
+      <c r="A11" s="33" t="s">
         <v>90</v>
       </c>
-      <c r="B11" s="21"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="21"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="30"/>
+      <c r="I11" s="30"/>
     </row>
     <row r="13" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B13" s="32" t="s">
+      <c r="B13" s="34" t="s">
         <v>641</v>
       </c>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="32"/>
       <c r="E13" s="10"/>
       <c r="F13" s="10"/>
       <c r="G13" s="10"/>
@@ -5321,11 +5299,11 @@
       <c r="A14" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="B14" s="32" t="s">
+      <c r="B14" s="34" t="s">
         <v>642</v>
       </c>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
+      <c r="C14" s="32"/>
+      <c r="D14" s="32"/>
       <c r="E14" s="10"/>
       <c r="F14" s="10"/>
       <c r="G14" s="10"/>
@@ -5340,18 +5318,18 @@
       <c r="A15" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="B15" s="32" t="s">
+      <c r="B15" s="34" t="s">
         <v>869</v>
       </c>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
       <c r="E15" s="10"/>
       <c r="F15" s="10"/>
       <c r="G15" s="10"/>
       <c r="H15" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="I15" s="41">
+      <c r="I15" s="20">
         <v>46305</v>
       </c>
     </row>
@@ -5359,61 +5337,61 @@
       <c r="A16" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="B16" s="32" t="s">
+      <c r="B16" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="30"/>
-      <c r="I16" s="30"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="32"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="32"/>
     </row>
     <row r="17" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="B17" s="32" t="s">
+      <c r="B17" s="34" t="s">
         <v>643</v>
       </c>
-      <c r="C17" s="30"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="30"/>
-      <c r="H17" s="30"/>
-      <c r="I17" s="30"/>
+      <c r="C17" s="32"/>
+      <c r="D17" s="32"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="32"/>
+      <c r="G17" s="32"/>
+      <c r="H17" s="32"/>
+      <c r="I17" s="32"/>
     </row>
     <row r="19" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="29" t="s">
+      <c r="A19" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="B19" s="29" t="s">
+      <c r="B19" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="C19" s="30"/>
-      <c r="D19" s="29" t="s">
+      <c r="C19" s="32"/>
+      <c r="D19" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="E19" s="29" t="s">
+      <c r="E19" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="F19" s="29" t="s">
+      <c r="F19" s="31" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="30"/>
+      <c r="A20" s="32"/>
       <c r="B20" s="5" t="s">
         <v>281</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="32"/>
     </row>
     <row r="21" spans="1:9" ht="86.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
@@ -5429,7 +5407,7 @@
         <v>647</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>5</v>
@@ -5449,7 +5427,7 @@
         <v>650</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>5</v>
@@ -5469,7 +5447,7 @@
         <v>650</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>5</v>
@@ -5489,7 +5467,7 @@
         <v>655</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>5</v>
@@ -5646,13 +5624,13 @@
         <v>679</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>897</v>
+        <v>906</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -5666,7 +5644,7 @@
         <v>679</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="E33" s="4">
         <v>400</v>
@@ -5686,13 +5664,13 @@
         <v>686</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="E34" s="4">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -5709,7 +5687,7 @@
         <v>690</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>5</v>
@@ -5717,17 +5695,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B16:I16"/>
-    <mergeCell ref="B17:I17"/>
-    <mergeCell ref="F4:I4"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="F6:I6"/>
-    <mergeCell ref="F7:I7"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="F9:I9"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="E2:F2"/>
@@ -5744,6 +5711,17 @@
     <mergeCell ref="E19:E20"/>
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="F19:F20"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B16:I16"/>
+    <mergeCell ref="B17:I17"/>
+    <mergeCell ref="F4:I4"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="F6:I6"/>
+    <mergeCell ref="F7:I7"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="F9:I9"/>
   </mergeCells>
   <conditionalFormatting sqref="F21:F35">
     <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
@@ -5783,44 +5761,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="37" t="s">
         <v>183</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
     </row>
     <row r="2" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="E2" s="37" t="s">
+      <c r="E2" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="F2" s="38"/>
+      <c r="F2" s="40"/>
     </row>
     <row r="3" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="B3" s="39" t="s">
+      <c r="B3" s="41" t="s">
         <v>187</v>
       </c>
-      <c r="C3" s="40"/>
+      <c r="C3" s="42"/>
       <c r="E3" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="F3" s="39" t="s">
+      <c r="F3" s="41" t="s">
         <v>187</v>
       </c>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
     </row>
     <row r="4" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
@@ -5906,27 +5884,27 @@
       <c r="I8" s="36"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="33" t="s">
         <v>90</v>
       </c>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="21"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="30"/>
+      <c r="I10" s="30"/>
     </row>
     <row r="12" spans="1:9" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B12" s="32" t="s">
+      <c r="B12" s="34" t="s">
         <v>700</v>
       </c>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
+      <c r="C12" s="32"/>
+      <c r="D12" s="32"/>
       <c r="E12" s="10"/>
       <c r="F12" s="10"/>
       <c r="G12" s="10"/>
@@ -5941,11 +5919,11 @@
       <c r="A13" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="B13" s="32" t="s">
+      <c r="B13" s="34" t="s">
         <v>701</v>
       </c>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="32"/>
       <c r="E13" s="10"/>
       <c r="F13" s="10"/>
       <c r="G13" s="10"/>
@@ -5960,18 +5938,18 @@
       <c r="A14" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="B14" s="32" t="s">
+      <c r="B14" s="34" t="s">
         <v>869</v>
       </c>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
+      <c r="C14" s="32"/>
+      <c r="D14" s="32"/>
       <c r="E14" s="10"/>
       <c r="F14" s="10"/>
       <c r="G14" s="10"/>
       <c r="H14" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="I14" s="41">
+      <c r="I14" s="20">
         <v>46305</v>
       </c>
     </row>
@@ -5979,61 +5957,61 @@
       <c r="A15" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="B15" s="32" t="s">
+      <c r="B15" s="34" t="s">
         <v>48</v>
       </c>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="30"/>
-      <c r="I15" s="30"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
     </row>
     <row r="16" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="B16" s="32" t="s">
+      <c r="B16" s="34" t="s">
         <v>702</v>
       </c>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="30"/>
-      <c r="I16" s="30"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="32"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="32"/>
     </row>
     <row r="18" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="29" t="s">
+      <c r="A18" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="B18" s="29" t="s">
+      <c r="B18" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="C18" s="30"/>
-      <c r="D18" s="29" t="s">
+      <c r="C18" s="32"/>
+      <c r="D18" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="E18" s="29" t="s">
+      <c r="E18" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="F18" s="29" t="s">
+      <c r="F18" s="31" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="30"/>
+      <c r="A19" s="32"/>
       <c r="B19" s="5" t="s">
         <v>281</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>703</v>
       </c>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
     </row>
     <row r="20" spans="1:6" ht="86.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
@@ -6069,7 +6047,7 @@
         <v>711</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>5</v>
@@ -6226,7 +6204,7 @@
         <v>741</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="E29" s="4">
         <v>200</v>
@@ -6257,6 +6235,14 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="F4:I4"/>
+    <mergeCell ref="B3:C3"/>
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="F5:I5"/>
@@ -6273,14 +6259,6 @@
     <mergeCell ref="A10:I10"/>
     <mergeCell ref="F7:I7"/>
     <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="F3:I3"/>
-    <mergeCell ref="F4:I4"/>
-    <mergeCell ref="B3:C3"/>
   </mergeCells>
   <conditionalFormatting sqref="F20:F30">
     <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
@@ -6320,44 +6298,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="37" t="s">
         <v>183</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
     </row>
     <row r="2" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="E2" s="37" t="s">
+      <c r="E2" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="F2" s="38"/>
+      <c r="F2" s="40"/>
     </row>
     <row r="3" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="B3" s="39" t="s">
+      <c r="B3" s="41" t="s">
         <v>187</v>
       </c>
-      <c r="C3" s="40"/>
+      <c r="C3" s="42"/>
       <c r="E3" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="F3" s="39" t="s">
+      <c r="F3" s="41" t="s">
         <v>187</v>
       </c>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
     </row>
     <row r="4" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
@@ -6436,27 +6414,27 @@
       <c r="I8" s="36"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="33" t="s">
         <v>90</v>
       </c>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="21"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="30"/>
+      <c r="I10" s="30"/>
     </row>
     <row r="12" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B12" s="32" t="s">
+      <c r="B12" s="34" t="s">
         <v>762</v>
       </c>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
+      <c r="C12" s="32"/>
+      <c r="D12" s="32"/>
       <c r="E12" s="10"/>
       <c r="F12" s="10"/>
       <c r="G12" s="10"/>
@@ -6471,11 +6449,11 @@
       <c r="A13" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="B13" s="32" t="s">
+      <c r="B13" s="34" t="s">
         <v>763</v>
       </c>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="32"/>
       <c r="E13" s="10"/>
       <c r="F13" s="10"/>
       <c r="G13" s="10"/>
@@ -6490,18 +6468,18 @@
       <c r="A14" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="B14" s="32" t="s">
+      <c r="B14" s="34" t="s">
         <v>869</v>
       </c>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
+      <c r="C14" s="32"/>
+      <c r="D14" s="32"/>
       <c r="E14" s="10"/>
       <c r="F14" s="10"/>
       <c r="G14" s="10"/>
       <c r="H14" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="I14" s="41">
+      <c r="I14" s="20">
         <v>46305</v>
       </c>
     </row>
@@ -6509,61 +6487,61 @@
       <c r="A15" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="B15" s="32" t="s">
+      <c r="B15" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="30"/>
-      <c r="I15" s="30"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
     </row>
     <row r="16" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="B16" s="32" t="s">
+      <c r="B16" s="34" t="s">
         <v>764</v>
       </c>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="30"/>
-      <c r="I16" s="30"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="32"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="32"/>
     </row>
     <row r="18" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="29" t="s">
+      <c r="A18" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="B18" s="29" t="s">
+      <c r="B18" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="C18" s="30"/>
-      <c r="D18" s="29" t="s">
+      <c r="C18" s="32"/>
+      <c r="D18" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="E18" s="29" t="s">
+      <c r="E18" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="F18" s="29" t="s">
+      <c r="F18" s="31" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="30"/>
+      <c r="A19" s="32"/>
       <c r="B19" s="5" t="s">
         <v>765</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>766</v>
       </c>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
     </row>
     <row r="20" spans="1:6" ht="107.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
@@ -6596,13 +6574,13 @@
         <v>773</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>906</v>
+        <v>900</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="86.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -6616,13 +6594,13 @@
         <v>776</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>904</v>
+        <v>899</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>903</v>
+        <v>907</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="128.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -6679,10 +6657,10 @@
         <v>403</v>
       </c>
       <c r="E25" s="4">
-        <v>201</v>
+        <v>403</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="107.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -6696,13 +6674,13 @@
         <v>790</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -6727,6 +6705,14 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="F4:I4"/>
+    <mergeCell ref="F7:I7"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="F5:I5"/>
     <mergeCell ref="A18:A19"/>
@@ -6742,14 +6728,6 @@
     <mergeCell ref="F6:I6"/>
     <mergeCell ref="B16:I16"/>
     <mergeCell ref="A10:I10"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="F3:I3"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="F4:I4"/>
-    <mergeCell ref="F7:I7"/>
   </mergeCells>
   <conditionalFormatting sqref="F20:F27">
     <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
@@ -6789,44 +6767,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="37" t="s">
         <v>183</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
     </row>
     <row r="2" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="E2" s="37" t="s">
+      <c r="E2" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="F2" s="38"/>
+      <c r="F2" s="40"/>
     </row>
     <row r="3" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="B3" s="39" t="s">
+      <c r="B3" s="41" t="s">
         <v>187</v>
       </c>
-      <c r="C3" s="40"/>
+      <c r="C3" s="42"/>
       <c r="E3" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="F3" s="39" t="s">
+      <c r="F3" s="41" t="s">
         <v>187</v>
       </c>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
     </row>
     <row r="4" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
@@ -6883,27 +6861,27 @@
       <c r="C7" s="36"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="31" t="s">
+      <c r="A9" s="33" t="s">
         <v>90</v>
       </c>
-      <c r="B9" s="21"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="21"/>
-      <c r="I9" s="21"/>
+      <c r="B9" s="30"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="30"/>
     </row>
     <row r="11" spans="1:9" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B11" s="32" t="s">
+      <c r="B11" s="34" t="s">
         <v>801</v>
       </c>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
+      <c r="C11" s="32"/>
+      <c r="D11" s="32"/>
       <c r="E11" s="10"/>
       <c r="F11" s="10"/>
       <c r="G11" s="10"/>
@@ -6918,11 +6896,11 @@
       <c r="A12" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="B12" s="32" t="s">
+      <c r="B12" s="34" t="s">
         <v>802</v>
       </c>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
+      <c r="C12" s="32"/>
+      <c r="D12" s="32"/>
       <c r="E12" s="10"/>
       <c r="F12" s="10"/>
       <c r="G12" s="10"/>
@@ -6937,18 +6915,18 @@
       <c r="A13" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="B13" s="32" t="s">
+      <c r="B13" s="34" t="s">
         <v>869</v>
       </c>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="32"/>
       <c r="E13" s="10"/>
       <c r="F13" s="10"/>
       <c r="G13" s="10"/>
       <c r="H13" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="I13" s="41">
+      <c r="I13" s="20">
         <v>46305</v>
       </c>
     </row>
@@ -6956,61 +6934,61 @@
       <c r="A14" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="B14" s="32" t="s">
+      <c r="B14" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="30"/>
-      <c r="I14" s="30"/>
+      <c r="C14" s="32"/>
+      <c r="D14" s="32"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="32"/>
+      <c r="I14" s="32"/>
     </row>
     <row r="15" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="B15" s="32" t="s">
+      <c r="B15" s="34" t="s">
         <v>803</v>
       </c>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="30"/>
-      <c r="I15" s="30"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
     </row>
     <row r="17" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="29" t="s">
+      <c r="A17" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="B17" s="29" t="s">
+      <c r="B17" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="C17" s="30"/>
-      <c r="D17" s="29" t="s">
+      <c r="C17" s="32"/>
+      <c r="D17" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="E17" s="29" t="s">
+      <c r="E17" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="F17" s="29" t="s">
+      <c r="F17" s="31" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="30"/>
+      <c r="A18" s="32"/>
       <c r="B18" s="5" t="s">
         <v>804</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>805</v>
       </c>
-      <c r="D18" s="30"/>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="32"/>
     </row>
     <row r="19" spans="1:6" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
@@ -7143,10 +7121,10 @@
         <v>830</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>908</v>
+        <v>902</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>907</v>
+        <v>901</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>5</v>
@@ -7163,17 +7141,27 @@
         <v>833</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>909</v>
+        <v>903</v>
       </c>
       <c r="E26" s="4">
-        <v>201</v>
+        <v>403</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="A9:I9"/>
+    <mergeCell ref="F5:I5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B3:C3"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="F17:F18"/>
     <mergeCell ref="F4:I4"/>
@@ -7185,29 +7173,8 @@
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B15:I15"/>
     <mergeCell ref="B13:D13"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="F3:I3"/>
-    <mergeCell ref="A9:I9"/>
-    <mergeCell ref="F5:I5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B3:C3"/>
   </mergeCells>
-  <conditionalFormatting sqref="F19:F25">
-    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
-      <formula>"Pass"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
-      <formula>"Fail"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="6" operator="equal">
-      <formula>"Block"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F26">
+  <conditionalFormatting sqref="F19:F26">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"Pass"</formula>
     </cfRule>
@@ -7240,10 +7207,9 @@
     <col min="2" max="2" width="11" customWidth="1"/>
     <col min="3" max="3" width="38" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="5" max="6" width="14" customWidth="1"/>
     <col min="7" max="9" width="11" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="10" max="10" width="13.140625" customWidth="1"/>
     <col min="11" max="11" width="74" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7307,10 +7273,12 @@
       <c r="C3" s="4" t="s">
         <v>846</v>
       </c>
-      <c r="D3" s="42">
+      <c r="D3" s="21">
         <v>46305</v>
       </c>
-      <c r="E3" s="4"/>
+      <c r="E3" s="20">
+        <v>46305</v>
+      </c>
       <c r="F3" s="11" t="s">
         <v>868</v>
       </c>
@@ -7323,7 +7291,9 @@
       <c r="I3" s="3" t="s">
         <v>848</v>
       </c>
-      <c r="J3" s="4"/>
+      <c r="J3" s="4" t="s">
+        <v>868</v>
+      </c>
       <c r="K3" s="4" t="s">
         <v>849</v>
       </c>
@@ -7338,10 +7308,12 @@
       <c r="C4" s="4" t="s">
         <v>851</v>
       </c>
-      <c r="D4" s="42">
+      <c r="D4" s="21">
         <v>46305</v>
       </c>
-      <c r="E4" s="4"/>
+      <c r="E4" s="20">
+        <v>46306</v>
+      </c>
       <c r="F4" s="11" t="s">
         <v>868</v>
       </c>
@@ -7354,9 +7326,11 @@
       <c r="I4" s="3" t="s">
         <v>848</v>
       </c>
-      <c r="J4" s="4"/>
+      <c r="J4" s="4" t="s">
+        <v>868</v>
+      </c>
       <c r="K4" s="4" t="s">
-        <v>910</v>
+        <v>904</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="128.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -7369,10 +7343,12 @@
       <c r="C5" s="4" t="s">
         <v>852</v>
       </c>
-      <c r="D5" s="42">
+      <c r="D5" s="21">
         <v>46305</v>
       </c>
-      <c r="E5" s="4"/>
+      <c r="E5" s="20">
+        <v>46307</v>
+      </c>
       <c r="F5" s="11" t="s">
         <v>868</v>
       </c>
@@ -7385,7 +7361,9 @@
       <c r="I5" s="3" t="s">
         <v>848</v>
       </c>
-      <c r="J5" s="4"/>
+      <c r="J5" s="4" t="s">
+        <v>868</v>
+      </c>
       <c r="K5" s="4" t="s">
         <v>853</v>
       </c>
@@ -7400,10 +7378,12 @@
       <c r="C6" s="4" t="s">
         <v>855</v>
       </c>
-      <c r="D6" s="42">
+      <c r="D6" s="21">
         <v>46305</v>
       </c>
-      <c r="E6" s="4"/>
+      <c r="E6" s="20">
+        <v>46308</v>
+      </c>
       <c r="F6" s="11" t="s">
         <v>868</v>
       </c>
@@ -7416,7 +7396,9 @@
       <c r="I6" s="3" t="s">
         <v>848</v>
       </c>
-      <c r="J6" s="4"/>
+      <c r="J6" s="4" t="s">
+        <v>868</v>
+      </c>
       <c r="K6" s="4" t="s">
         <v>857</v>
       </c>
@@ -7431,10 +7413,12 @@
       <c r="C7" s="4" t="s">
         <v>859</v>
       </c>
-      <c r="D7" s="42">
+      <c r="D7" s="21">
         <v>46305</v>
       </c>
-      <c r="E7" s="4"/>
+      <c r="E7" s="20">
+        <v>46309</v>
+      </c>
       <c r="F7" s="11" t="s">
         <v>868</v>
       </c>
@@ -7447,7 +7431,9 @@
       <c r="I7" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="J7" s="4"/>
+      <c r="J7" s="4" t="s">
+        <v>868</v>
+      </c>
       <c r="K7" s="4" t="s">
         <v>860</v>
       </c>
@@ -7462,10 +7448,12 @@
       <c r="C8" s="4" t="s">
         <v>862</v>
       </c>
-      <c r="D8" s="42">
+      <c r="D8" s="21">
         <v>46305</v>
       </c>
-      <c r="E8" s="4"/>
+      <c r="E8" s="20">
+        <v>46310</v>
+      </c>
       <c r="F8" s="11" t="s">
         <v>868</v>
       </c>
@@ -7478,9 +7466,11 @@
       <c r="I8" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="J8" s="4"/>
+      <c r="J8" s="4" t="s">
+        <v>868</v>
+      </c>
       <c r="K8" s="4" t="s">
-        <v>911</v>
+        <v>905</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="86.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -7493,10 +7483,12 @@
       <c r="C9" s="4" t="s">
         <v>863</v>
       </c>
-      <c r="D9" s="42">
+      <c r="D9" s="21">
         <v>46305</v>
       </c>
-      <c r="E9" s="4"/>
+      <c r="E9" s="20">
+        <v>46311</v>
+      </c>
       <c r="F9" s="11" t="s">
         <v>868</v>
       </c>
@@ -7509,7 +7501,9 @@
       <c r="I9" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="J9" s="4"/>
+      <c r="J9" s="4" t="s">
+        <v>868</v>
+      </c>
       <c r="K9" s="4" t="s">
         <v>865</v>
       </c>
@@ -7537,11 +7531,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
     </row>
     <row r="2" spans="1:3" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -7720,15 +7714,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="33" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
       <c r="J1" s="4"/>
       <c r="K1" s="5" t="s">
         <v>91</v>
@@ -7764,12 +7758,12 @@
       <c r="A3" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
       <c r="F3" s="9" t="s">
         <v>102</v>
       </c>
@@ -7796,12 +7790,12 @@
       <c r="A4" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="34" t="s">
         <v>109</v>
       </c>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
       <c r="F4" s="9" t="s">
         <v>110</v>
       </c>
@@ -7828,16 +7822,16 @@
       <c r="A5" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="34" t="s">
         <v>869</v>
       </c>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="32"/>
+      <c r="E5" s="32"/>
       <c r="F5" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="G5" s="41">
+      <c r="G5" s="20">
         <v>46305</v>
       </c>
     </row>
@@ -7845,49 +7839,49 @@
       <c r="A6" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="30"/>
-      <c r="D6" s="30"/>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="30"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="32"/>
     </row>
     <row r="7" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="34" t="s">
         <v>120</v>
       </c>
-      <c r="C7" s="30"/>
-      <c r="D7" s="30"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="30"/>
+      <c r="C7" s="32"/>
+      <c r="D7" s="32"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="32"/>
     </row>
     <row r="9" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="29" t="s">
+      <c r="A9" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="C9" s="30"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="29" t="s">
+      <c r="C9" s="32"/>
+      <c r="D9" s="32"/>
+      <c r="E9" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="F9" s="29" t="s">
+      <c r="F9" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="G9" s="29" t="s">
+      <c r="G9" s="31" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="30"/>
+      <c r="A10" s="32"/>
       <c r="B10" s="5" t="s">
         <v>126</v>
       </c>
@@ -7897,9 +7891,9 @@
       <c r="D10" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="E10" s="30"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="30"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="32"/>
+      <c r="G10" s="32"/>
     </row>
     <row r="11" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
@@ -8368,44 +8362,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="37" t="s">
         <v>183</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
     </row>
     <row r="2" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="E2" s="37" t="s">
+      <c r="E2" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="F2" s="38"/>
+      <c r="F2" s="40"/>
     </row>
     <row r="3" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="B3" s="39" t="s">
+      <c r="B3" s="41" t="s">
         <v>187</v>
       </c>
-      <c r="C3" s="40"/>
+      <c r="C3" s="42"/>
       <c r="E3" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="F3" s="39" t="s">
+      <c r="F3" s="41" t="s">
         <v>187</v>
       </c>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
     </row>
     <row r="4" spans="1:9" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
@@ -8489,27 +8483,27 @@
       <c r="C9" s="36"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="31" t="s">
+      <c r="A11" s="33" t="s">
         <v>90</v>
       </c>
-      <c r="B11" s="21"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="21"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="30"/>
+      <c r="I11" s="30"/>
     </row>
     <row r="13" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B13" s="32" t="s">
+      <c r="B13" s="34" t="s">
         <v>206</v>
       </c>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="32"/>
       <c r="E13" s="10"/>
       <c r="F13" s="10"/>
       <c r="G13" s="10"/>
@@ -8524,11 +8518,11 @@
       <c r="A14" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="B14" s="32" t="s">
+      <c r="B14" s="34" t="s">
         <v>207</v>
       </c>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
+      <c r="C14" s="32"/>
+      <c r="D14" s="32"/>
       <c r="E14" s="10"/>
       <c r="F14" s="10"/>
       <c r="G14" s="10"/>
@@ -8543,18 +8537,18 @@
       <c r="A15" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="B15" s="32" t="s">
+      <c r="B15" s="34" t="s">
         <v>869</v>
       </c>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
       <c r="E15" s="10"/>
       <c r="F15" s="10"/>
       <c r="G15" s="10"/>
       <c r="H15" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="I15" s="41">
+      <c r="I15" s="20">
         <v>46305</v>
       </c>
     </row>
@@ -8562,61 +8556,61 @@
       <c r="A16" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="B16" s="32" t="s">
+      <c r="B16" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="30"/>
-      <c r="I16" s="30"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="32"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="32"/>
     </row>
     <row r="17" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="B17" s="32" t="s">
+      <c r="B17" s="34" t="s">
         <v>208</v>
       </c>
-      <c r="C17" s="30"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="30"/>
-      <c r="H17" s="30"/>
-      <c r="I17" s="30"/>
+      <c r="C17" s="32"/>
+      <c r="D17" s="32"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="32"/>
+      <c r="G17" s="32"/>
+      <c r="H17" s="32"/>
+      <c r="I17" s="32"/>
     </row>
     <row r="19" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="29" t="s">
+      <c r="A19" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="B19" s="29" t="s">
+      <c r="B19" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="C19" s="30"/>
-      <c r="D19" s="29" t="s">
+      <c r="C19" s="32"/>
+      <c r="D19" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="E19" s="29" t="s">
+      <c r="E19" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="F19" s="29" t="s">
+      <c r="F19" s="31" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="30"/>
+      <c r="A20" s="32"/>
       <c r="B20" s="5" t="s">
         <v>209</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="32"/>
     </row>
     <row r="21" spans="1:9" ht="107.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
@@ -8632,7 +8626,7 @@
         <v>214</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>5</v>
@@ -8652,7 +8646,7 @@
         <v>218</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>5</v>
@@ -8672,7 +8666,7 @@
         <v>222</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>5</v>
@@ -8692,7 +8686,7 @@
         <v>225</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>5</v>
@@ -8712,7 +8706,7 @@
         <v>228</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>5</v>
@@ -8732,7 +8726,7 @@
         <v>231</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>5</v>
@@ -8752,7 +8746,7 @@
         <v>235</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>5</v>
@@ -8772,7 +8766,7 @@
         <v>238</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>5</v>
@@ -8792,7 +8786,7 @@
         <v>242</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>5</v>
@@ -8812,7 +8806,7 @@
         <v>245</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>5</v>
@@ -8832,7 +8826,7 @@
         <v>249</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>5</v>
@@ -8852,7 +8846,7 @@
         <v>253</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>5</v>
@@ -8872,7 +8866,7 @@
         <v>257</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>5</v>
@@ -8892,7 +8886,7 @@
         <v>261</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>5</v>
@@ -8900,14 +8894,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="E19:E20"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="F19:F20"/>
-    <mergeCell ref="B17:I17"/>
-    <mergeCell ref="F4:I4"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="F6:I6"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="E2:F2"/>
@@ -8924,6 +8910,14 @@
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B16:I16"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="B17:I17"/>
+    <mergeCell ref="F4:I4"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="F6:I6"/>
   </mergeCells>
   <conditionalFormatting sqref="F21:F34">
     <cfRule type="cellIs" dxfId="35" priority="1" operator="equal">
@@ -8964,44 +8958,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="37" t="s">
         <v>183</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
     </row>
     <row r="2" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="E2" s="37" t="s">
+      <c r="E2" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="F2" s="38"/>
+      <c r="F2" s="40"/>
     </row>
     <row r="3" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="B3" s="39" t="s">
+      <c r="B3" s="41" t="s">
         <v>187</v>
       </c>
-      <c r="C3" s="40"/>
+      <c r="C3" s="42"/>
       <c r="E3" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="F3" s="39" t="s">
+      <c r="F3" s="41" t="s">
         <v>187</v>
       </c>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
     </row>
     <row r="4" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
@@ -9120,27 +9114,27 @@
       <c r="I11" s="36"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="31" t="s">
+      <c r="A13" s="33" t="s">
         <v>90</v>
       </c>
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
+      <c r="B13" s="30"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="30"/>
+      <c r="H13" s="30"/>
+      <c r="I13" s="30"/>
     </row>
     <row r="15" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B15" s="32" t="s">
+      <c r="B15" s="34" t="s">
         <v>279</v>
       </c>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
       <c r="E15" s="10"/>
       <c r="F15" s="10"/>
       <c r="G15" s="10"/>
@@ -9155,11 +9149,11 @@
       <c r="A16" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="B16" s="32" t="s">
+      <c r="B16" s="34" t="s">
         <v>207</v>
       </c>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
       <c r="G16" s="10"/>
@@ -9174,18 +9168,18 @@
       <c r="A17" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="B17" s="32" t="s">
+      <c r="B17" s="34" t="s">
         <v>869</v>
       </c>
-      <c r="C17" s="30"/>
-      <c r="D17" s="30"/>
+      <c r="C17" s="32"/>
+      <c r="D17" s="32"/>
       <c r="E17" s="10"/>
       <c r="F17" s="10"/>
       <c r="G17" s="10"/>
       <c r="H17" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="I17" s="41">
+      <c r="I17" s="20">
         <v>46305</v>
       </c>
     </row>
@@ -9193,61 +9187,61 @@
       <c r="A18" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="B18" s="32" t="s">
+      <c r="B18" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="C18" s="30"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="30"/>
-      <c r="H18" s="30"/>
-      <c r="I18" s="30"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="32"/>
+      <c r="G18" s="32"/>
+      <c r="H18" s="32"/>
+      <c r="I18" s="32"/>
     </row>
     <row r="19" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="B19" s="32" t="s">
+      <c r="B19" s="34" t="s">
         <v>280</v>
       </c>
-      <c r="C19" s="30"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="30"/>
-      <c r="H19" s="30"/>
-      <c r="I19" s="30"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="32"/>
+      <c r="I19" s="32"/>
     </row>
     <row r="21" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="29" t="s">
+      <c r="A21" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="B21" s="29" t="s">
+      <c r="B21" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="C21" s="30"/>
-      <c r="D21" s="29" t="s">
+      <c r="C21" s="32"/>
+      <c r="D21" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="E21" s="29" t="s">
+      <c r="E21" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="F21" s="29" t="s">
+      <c r="F21" s="31" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="30"/>
+      <c r="A22" s="32"/>
       <c r="B22" s="5" t="s">
         <v>281</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="D22" s="30"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="30"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="32"/>
     </row>
     <row r="23" spans="1:9" ht="86.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
@@ -9483,7 +9477,7 @@
         <v>323</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>5</v>
@@ -9491,18 +9485,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="F9:I9"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B18:I18"/>
-    <mergeCell ref="F4:I4"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="F11:I11"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="F10:I10"/>
-    <mergeCell ref="F6:I6"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="D21:D22"/>
@@ -9518,6 +9500,18 @@
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B19:I19"/>
     <mergeCell ref="E21:E22"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="F9:I9"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B18:I18"/>
+    <mergeCell ref="F4:I4"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="F11:I11"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="F10:I10"/>
+    <mergeCell ref="F6:I6"/>
   </mergeCells>
   <conditionalFormatting sqref="F23:F34">
     <cfRule type="cellIs" dxfId="32" priority="1" operator="equal">
@@ -9826,26 +9820,26 @@
       <c r="G15" s="23"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="31" t="s">
+      <c r="A17" s="33" t="s">
         <v>90</v>
       </c>
-      <c r="B17" s="21"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
+      <c r="B17" s="30"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="30"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="30"/>
     </row>
     <row r="19" spans="1:7" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B19" s="32" t="s">
+      <c r="B19" s="34" t="s">
         <v>351</v>
       </c>
-      <c r="C19" s="30"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
       <c r="F19" s="9" t="s">
         <v>102</v>
       </c>
@@ -9857,12 +9851,12 @@
       <c r="A20" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="B20" s="32" t="s">
+      <c r="B20" s="34" t="s">
         <v>352</v>
       </c>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
+      <c r="C20" s="32"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="32"/>
       <c r="F20" s="9" t="s">
         <v>110</v>
       </c>
@@ -9874,16 +9868,16 @@
       <c r="A21" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="B21" s="32" t="s">
+      <c r="B21" s="34" t="s">
         <v>869</v>
       </c>
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
+      <c r="C21" s="32"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="32"/>
       <c r="F21" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="G21" s="41">
+      <c r="G21" s="20">
         <v>46305</v>
       </c>
     </row>
@@ -9891,61 +9885,61 @@
       <c r="A22" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="B22" s="32" t="s">
+      <c r="B22" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="C22" s="30"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="30"/>
-      <c r="G22" s="30"/>
+      <c r="C22" s="32"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="32"/>
+      <c r="G22" s="32"/>
     </row>
     <row r="23" spans="1:7" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="B23" s="32" t="s">
+      <c r="B23" s="34" t="s">
         <v>353</v>
       </c>
-      <c r="C23" s="30"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="30"/>
-      <c r="G23" s="30"/>
+      <c r="C23" s="32"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="32"/>
+      <c r="G23" s="32"/>
     </row>
     <row r="25" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="29" t="s">
+      <c r="A25" s="31" t="s">
         <v>354</v>
       </c>
-      <c r="B25" s="29" t="s">
+      <c r="B25" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="C25" s="29" t="s">
+      <c r="C25" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="D25" s="30"/>
-      <c r="E25" s="29" t="s">
+      <c r="D25" s="32"/>
+      <c r="E25" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="F25" s="29" t="s">
+      <c r="F25" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="G25" s="29" t="s">
+      <c r="G25" s="31" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="30"/>
-      <c r="B26" s="30"/>
+      <c r="A26" s="32"/>
+      <c r="B26" s="32"/>
       <c r="C26" s="5" t="s">
         <v>355</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="E26" s="30"/>
-      <c r="F26" s="30"/>
-      <c r="G26" s="30"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="32"/>
     </row>
     <row r="27" spans="1:7" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
@@ -9963,7 +9957,9 @@
       <c r="E27" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="F27" s="4"/>
+      <c r="F27" s="4" t="s">
+        <v>883</v>
+      </c>
       <c r="G27" s="3" t="s">
         <v>5</v>
       </c>
@@ -9984,7 +9980,9 @@
       <c r="E28" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="F28" s="4"/>
+      <c r="F28" s="4" t="s">
+        <v>883</v>
+      </c>
       <c r="G28" s="3" t="s">
         <v>5</v>
       </c>
@@ -10005,7 +10003,9 @@
       <c r="E29" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="F29" s="4"/>
+      <c r="F29" s="4" t="s">
+        <v>883</v>
+      </c>
       <c r="G29" s="3" t="s">
         <v>5</v>
       </c>
@@ -10026,7 +10026,9 @@
       <c r="E30" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="F30" s="4"/>
+      <c r="F30" s="4" t="s">
+        <v>883</v>
+      </c>
       <c r="G30" s="3" t="s">
         <v>5</v>
       </c>
@@ -10047,7 +10049,9 @@
       <c r="E31" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="F31" s="4"/>
+      <c r="F31" s="4" t="s">
+        <v>883</v>
+      </c>
       <c r="G31" s="3" t="s">
         <v>5</v>
       </c>
@@ -10068,7 +10072,9 @@
       <c r="E32" s="4" t="s">
         <v>371</v>
       </c>
-      <c r="F32" s="4"/>
+      <c r="F32" s="4">
+        <v>401</v>
+      </c>
       <c r="G32" s="3" t="s">
         <v>5</v>
       </c>
@@ -10089,7 +10095,9 @@
       <c r="E33" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="F33" s="4"/>
+      <c r="F33" s="4" t="s">
+        <v>883</v>
+      </c>
       <c r="G33" s="3" t="s">
         <v>5</v>
       </c>
@@ -10110,7 +10118,9 @@
       <c r="E34" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="F34" s="4"/>
+      <c r="F34" s="4" t="s">
+        <v>883</v>
+      </c>
       <c r="G34" s="3" t="s">
         <v>5</v>
       </c>
@@ -10131,7 +10141,9 @@
       <c r="E35" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="F35" s="4"/>
+      <c r="F35" s="4" t="s">
+        <v>883</v>
+      </c>
       <c r="G35" s="3" t="s">
         <v>5</v>
       </c>
@@ -10152,7 +10164,9 @@
       <c r="E36" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="F36" s="4"/>
+      <c r="F36" s="4" t="s">
+        <v>883</v>
+      </c>
       <c r="G36" s="3" t="s">
         <v>5</v>
       </c>
@@ -10243,7 +10257,7 @@
         <v>360</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>5</v>
@@ -10266,7 +10280,7 @@
         <v>360</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>5</v>
@@ -10381,7 +10395,7 @@
         <v>360</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>5</v>
@@ -10496,7 +10510,7 @@
         <v>360</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>5</v>
@@ -10588,7 +10602,7 @@
         <v>360</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>5</v>
@@ -10611,7 +10625,7 @@
         <v>360</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="G56" s="3" t="s">
         <v>5</v>
@@ -10703,7 +10717,7 @@
         <v>360</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>5</v>
@@ -10726,7 +10740,7 @@
         <v>360</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>5</v>
@@ -10818,7 +10832,7 @@
         <v>360</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="G65" s="3" t="s">
         <v>5</v>
@@ -10841,7 +10855,7 @@
         <v>360</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>5</v>
@@ -10887,10 +10901,10 @@
         <v>403</v>
       </c>
       <c r="F68" s="4">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -10910,10 +10924,10 @@
         <v>403</v>
       </c>
       <c r="F69" s="4">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -10933,7 +10947,7 @@
         <v>360</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="G70" s="3" t="s">
         <v>5</v>
@@ -10956,7 +10970,7 @@
         <v>360</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="G71" s="3" t="s">
         <v>5</v>
@@ -11002,10 +11016,10 @@
         <v>403</v>
       </c>
       <c r="F73" s="4">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -11025,7 +11039,7 @@
         <v>360</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>5</v>
@@ -11048,7 +11062,7 @@
         <v>360</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>5</v>
@@ -11071,7 +11085,7 @@
         <v>360</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>5</v>
@@ -11131,44 +11145,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="37" t="s">
         <v>183</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
     </row>
     <row r="2" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="E2" s="37" t="s">
+      <c r="E2" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="F2" s="38"/>
+      <c r="F2" s="40"/>
     </row>
     <row r="3" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="B3" s="39" t="s">
+      <c r="B3" s="41" t="s">
         <v>187</v>
       </c>
-      <c r="C3" s="40"/>
+      <c r="C3" s="42"/>
       <c r="E3" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="F3" s="39" t="s">
+      <c r="F3" s="41" t="s">
         <v>187</v>
       </c>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
     </row>
     <row r="4" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
@@ -11277,27 +11291,27 @@
       <c r="I12" s="36"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="31" t="s">
+      <c r="A14" s="33" t="s">
         <v>90</v>
       </c>
-      <c r="B14" s="21"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="21"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="30"/>
+      <c r="H14" s="30"/>
+      <c r="I14" s="30"/>
     </row>
     <row r="16" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B16" s="32" t="s">
+      <c r="B16" s="34" t="s">
         <v>436</v>
       </c>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
       <c r="G16" s="10"/>
@@ -11312,11 +11326,11 @@
       <c r="A17" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="B17" s="32" t="s">
+      <c r="B17" s="34" t="s">
         <v>207</v>
       </c>
-      <c r="C17" s="30"/>
-      <c r="D17" s="30"/>
+      <c r="C17" s="32"/>
+      <c r="D17" s="32"/>
       <c r="E17" s="10"/>
       <c r="F17" s="10"/>
       <c r="G17" s="10"/>
@@ -11331,18 +11345,18 @@
       <c r="A18" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="B18" s="32" t="s">
+      <c r="B18" s="34" t="s">
         <v>869</v>
       </c>
-      <c r="C18" s="30"/>
-      <c r="D18" s="30"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="32"/>
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
       <c r="G18" s="10"/>
       <c r="H18" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="I18" s="41">
+      <c r="I18" s="20">
         <v>46305</v>
       </c>
     </row>
@@ -11350,61 +11364,61 @@
       <c r="A19" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="B19" s="32" t="s">
+      <c r="B19" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="C19" s="30"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="30"/>
-      <c r="H19" s="30"/>
-      <c r="I19" s="30"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="32"/>
+      <c r="I19" s="32"/>
     </row>
     <row r="20" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="B20" s="32" t="s">
+      <c r="B20" s="34" t="s">
         <v>437</v>
       </c>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="30"/>
-      <c r="H20" s="30"/>
-      <c r="I20" s="30"/>
+      <c r="C20" s="32"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="32"/>
+      <c r="H20" s="32"/>
+      <c r="I20" s="32"/>
     </row>
     <row r="22" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="29" t="s">
+      <c r="A22" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="B22" s="29" t="s">
+      <c r="B22" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="C22" s="30"/>
-      <c r="D22" s="29" t="s">
+      <c r="C22" s="32"/>
+      <c r="D22" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="E22" s="29" t="s">
+      <c r="E22" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="F22" s="29" t="s">
+      <c r="F22" s="31" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="30"/>
+      <c r="A23" s="32"/>
       <c r="B23" s="5" t="s">
         <v>438</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="D23" s="30"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="30"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="32"/>
     </row>
     <row r="24" spans="1:9" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
@@ -11420,7 +11434,7 @@
         <v>442</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>5</v>
@@ -11440,7 +11454,7 @@
         <v>445</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>5</v>
@@ -11537,13 +11551,13 @@
         <v>461</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="E30" s="4">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="86.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -11557,13 +11571,13 @@
         <v>463</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="E31" s="4">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -11608,16 +11622,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="B20:I20"/>
-    <mergeCell ref="F4:I4"/>
-    <mergeCell ref="A14:I14"/>
-    <mergeCell ref="F11:I11"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="F10:I10"/>
-    <mergeCell ref="F6:I6"/>
-    <mergeCell ref="F7:I7"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="D22:D23"/>
@@ -11633,6 +11637,16 @@
     <mergeCell ref="F9:I9"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B17:D17"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="B20:I20"/>
+    <mergeCell ref="F4:I4"/>
+    <mergeCell ref="A14:I14"/>
+    <mergeCell ref="F11:I11"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="F10:I10"/>
+    <mergeCell ref="F6:I6"/>
+    <mergeCell ref="F7:I7"/>
   </mergeCells>
   <conditionalFormatting sqref="F24:F33">
     <cfRule type="cellIs" dxfId="26" priority="1" operator="equal">
@@ -11899,26 +11913,26 @@
       <c r="G13" s="23"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="31" t="s">
+      <c r="A15" s="33" t="s">
         <v>90</v>
       </c>
-      <c r="B15" s="21"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
+      <c r="B15" s="30"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="30"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="30"/>
     </row>
     <row r="17" spans="1:7" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B17" s="32" t="s">
+      <c r="B17" s="34" t="s">
         <v>484</v>
       </c>
-      <c r="C17" s="30"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="30"/>
+      <c r="C17" s="32"/>
+      <c r="D17" s="32"/>
+      <c r="E17" s="32"/>
       <c r="F17" s="9" t="s">
         <v>102</v>
       </c>
@@ -11930,12 +11944,12 @@
       <c r="A18" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="B18" s="32" t="s">
+      <c r="B18" s="34" t="s">
         <v>485</v>
       </c>
-      <c r="C18" s="30"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="30"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="32"/>
       <c r="F18" s="9" t="s">
         <v>110</v>
       </c>
@@ -11947,16 +11961,16 @@
       <c r="A19" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="B19" s="32" t="s">
+      <c r="B19" s="34" t="s">
         <v>869</v>
       </c>
-      <c r="C19" s="30"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
       <c r="F19" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="G19" s="41">
+      <c r="G19" s="20">
         <v>46305</v>
       </c>
     </row>
@@ -11964,61 +11978,61 @@
       <c r="A20" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="B20" s="32" t="s">
+      <c r="B20" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="30"/>
+      <c r="C20" s="32"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="32"/>
     </row>
     <row r="21" spans="1:7" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="B21" s="32" t="s">
+      <c r="B21" s="34" t="s">
         <v>486</v>
       </c>
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="30"/>
+      <c r="C21" s="32"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="32"/>
     </row>
     <row r="23" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="29" t="s">
+      <c r="A23" s="31" t="s">
         <v>354</v>
       </c>
-      <c r="B23" s="29" t="s">
+      <c r="B23" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="C23" s="29" t="s">
+      <c r="C23" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="D23" s="30"/>
-      <c r="E23" s="29" t="s">
+      <c r="D23" s="32"/>
+      <c r="E23" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="F23" s="29" t="s">
+      <c r="F23" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="G23" s="29" t="s">
+      <c r="G23" s="31" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="30"/>
-      <c r="B24" s="30"/>
+      <c r="A24" s="32"/>
+      <c r="B24" s="32"/>
       <c r="C24" s="5" t="s">
         <v>487</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="E24" s="30"/>
-      <c r="F24" s="30"/>
-      <c r="G24" s="30"/>
+      <c r="E24" s="32"/>
+      <c r="F24" s="32"/>
+      <c r="G24" s="32"/>
     </row>
     <row r="25" spans="1:7" ht="86.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">

--- a/test/FIWDEE_IntegrationTest_Design.xlsx
+++ b/test/FIWDEE_IntegrationTest_Design.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\ProjectPOS\FIWDEE-CP353002-69_1PrinciplesOfSoftwareDesign\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAC00310-1326-44E8-90F7-B7BFCEB8B029}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4227400A-8ED7-4AD7-933B-3A00523F3264}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Summary" sheetId="1" r:id="rId1"/>
@@ -2998,14 +2998,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3018,28 +3018,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="39">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="36">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -4551,13 +4530,13 @@
     <mergeCell ref="F9:F10"/>
   </mergeCells>
   <conditionalFormatting sqref="F11:F20">
-    <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
       <formula>"Pass"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="2" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="3" operator="equal">
       <formula>"Block"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5079,13 +5058,13 @@
     <mergeCell ref="C21:D21"/>
   </mergeCells>
   <conditionalFormatting sqref="G23:G30">
-    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
       <formula>"Pass"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="2" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="3" operator="equal">
       <formula>"Block"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5116,17 +5095,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="35" t="s">
         <v>183</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
     </row>
     <row r="2" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
@@ -5159,109 +5138,109 @@
       <c r="A4" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="37" t="s">
         <v>629</v>
       </c>
-      <c r="C4" s="36"/>
+      <c r="C4" s="38"/>
       <c r="E4" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="F4" s="35" t="s">
+      <c r="F4" s="37" t="s">
         <v>630</v>
       </c>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="36"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
     </row>
     <row r="5" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="B5" s="35" t="s">
+      <c r="B5" s="37" t="s">
         <v>631</v>
       </c>
-      <c r="C5" s="36"/>
+      <c r="C5" s="38"/>
       <c r="E5" s="15" t="s">
         <v>194</v>
       </c>
-      <c r="F5" s="35" t="s">
+      <c r="F5" s="37" t="s">
         <v>632</v>
       </c>
-      <c r="G5" s="36"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="36"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="38"/>
+      <c r="I5" s="38"/>
     </row>
     <row r="6" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="B6" s="35" t="s">
+      <c r="B6" s="37" t="s">
         <v>633</v>
       </c>
-      <c r="C6" s="36"/>
+      <c r="C6" s="38"/>
       <c r="E6" s="15" t="s">
         <v>198</v>
       </c>
-      <c r="F6" s="35" t="s">
+      <c r="F6" s="37" t="s">
         <v>634</v>
       </c>
-      <c r="G6" s="36"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="36"/>
+      <c r="G6" s="38"/>
+      <c r="H6" s="38"/>
+      <c r="I6" s="38"/>
     </row>
     <row r="7" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
         <v>200</v>
       </c>
-      <c r="B7" s="35" t="s">
+      <c r="B7" s="37" t="s">
         <v>635</v>
       </c>
-      <c r="C7" s="36"/>
+      <c r="C7" s="38"/>
       <c r="E7" s="15" t="s">
         <v>269</v>
       </c>
-      <c r="F7" s="35" t="s">
+      <c r="F7" s="37" t="s">
         <v>636</v>
       </c>
-      <c r="G7" s="36"/>
-      <c r="H7" s="36"/>
-      <c r="I7" s="36"/>
+      <c r="G7" s="38"/>
+      <c r="H7" s="38"/>
+      <c r="I7" s="38"/>
     </row>
     <row r="8" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
         <v>202</v>
       </c>
-      <c r="B8" s="35" t="s">
+      <c r="B8" s="37" t="s">
         <v>637</v>
       </c>
-      <c r="C8" s="36"/>
+      <c r="C8" s="38"/>
       <c r="E8" s="15" t="s">
         <v>271</v>
       </c>
-      <c r="F8" s="35" t="s">
+      <c r="F8" s="37" t="s">
         <v>638</v>
       </c>
-      <c r="G8" s="36"/>
-      <c r="H8" s="36"/>
-      <c r="I8" s="36"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="38"/>
+      <c r="I8" s="38"/>
     </row>
     <row r="9" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
         <v>204</v>
       </c>
-      <c r="B9" s="35" t="s">
+      <c r="B9" s="37" t="s">
         <v>639</v>
       </c>
-      <c r="C9" s="36"/>
+      <c r="C9" s="38"/>
       <c r="E9" s="15" t="s">
         <v>273</v>
       </c>
-      <c r="F9" s="35" t="s">
+      <c r="F9" s="37" t="s">
         <v>640</v>
       </c>
-      <c r="G9" s="36"/>
-      <c r="H9" s="36"/>
-      <c r="I9" s="36"/>
+      <c r="G9" s="38"/>
+      <c r="H9" s="38"/>
+      <c r="I9" s="38"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="33" t="s">
@@ -5695,6 +5674,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B16:I16"/>
+    <mergeCell ref="B17:I17"/>
+    <mergeCell ref="F4:I4"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="F6:I6"/>
+    <mergeCell ref="F7:I7"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="F9:I9"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="E2:F2"/>
@@ -5711,26 +5701,15 @@
     <mergeCell ref="E19:E20"/>
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="F19:F20"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B16:I16"/>
-    <mergeCell ref="B17:I17"/>
-    <mergeCell ref="F4:I4"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="F6:I6"/>
-    <mergeCell ref="F7:I7"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="F9:I9"/>
   </mergeCells>
   <conditionalFormatting sqref="F21:F35">
-    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
       <formula>"Pass"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
       <formula>"Block"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5761,17 +5740,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="35" t="s">
         <v>183</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
     </row>
     <row r="2" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
@@ -5804,84 +5783,84 @@
       <c r="A4" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="37" t="s">
         <v>691</v>
       </c>
-      <c r="C4" s="36"/>
+      <c r="C4" s="38"/>
       <c r="E4" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="F4" s="35" t="s">
+      <c r="F4" s="37" t="s">
         <v>692</v>
       </c>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="36"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
     </row>
     <row r="5" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="B5" s="35" t="s">
+      <c r="B5" s="37" t="s">
         <v>693</v>
       </c>
-      <c r="C5" s="36"/>
+      <c r="C5" s="38"/>
       <c r="E5" s="15" t="s">
         <v>194</v>
       </c>
-      <c r="F5" s="35" t="s">
+      <c r="F5" s="37" t="s">
         <v>694</v>
       </c>
-      <c r="G5" s="36"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="36"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="38"/>
+      <c r="I5" s="38"/>
     </row>
     <row r="6" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="B6" s="35" t="s">
+      <c r="B6" s="37" t="s">
         <v>695</v>
       </c>
-      <c r="C6" s="36"/>
+      <c r="C6" s="38"/>
       <c r="E6" s="15" t="s">
         <v>198</v>
       </c>
-      <c r="F6" s="35" t="s">
+      <c r="F6" s="37" t="s">
         <v>696</v>
       </c>
-      <c r="G6" s="36"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="36"/>
+      <c r="G6" s="38"/>
+      <c r="H6" s="38"/>
+      <c r="I6" s="38"/>
     </row>
     <row r="7" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
         <v>200</v>
       </c>
-      <c r="B7" s="35" t="s">
+      <c r="B7" s="37" t="s">
         <v>697</v>
       </c>
-      <c r="C7" s="36"/>
+      <c r="C7" s="38"/>
       <c r="E7" s="15" t="s">
         <v>269</v>
       </c>
-      <c r="F7" s="35" t="s">
+      <c r="F7" s="37" t="s">
         <v>698</v>
       </c>
-      <c r="G7" s="36"/>
-      <c r="H7" s="36"/>
-      <c r="I7" s="36"/>
+      <c r="G7" s="38"/>
+      <c r="H7" s="38"/>
+      <c r="I7" s="38"/>
     </row>
     <row r="8" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E8" s="15" t="s">
         <v>271</v>
       </c>
-      <c r="F8" s="35" t="s">
+      <c r="F8" s="37" t="s">
         <v>699</v>
       </c>
-      <c r="G8" s="36"/>
-      <c r="H8" s="36"/>
-      <c r="I8" s="36"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="38"/>
+      <c r="I8" s="38"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="33" t="s">
@@ -6235,14 +6214,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="F3:I3"/>
-    <mergeCell ref="F4:I4"/>
-    <mergeCell ref="B3:C3"/>
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="F5:I5"/>
@@ -6259,15 +6230,23 @@
     <mergeCell ref="A10:I10"/>
     <mergeCell ref="F7:I7"/>
     <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="F4:I4"/>
+    <mergeCell ref="B3:C3"/>
   </mergeCells>
   <conditionalFormatting sqref="F20:F30">
-    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
       <formula>"Pass"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
       <formula>"Block"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6298,17 +6277,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="35" t="s">
         <v>183</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
     </row>
     <row r="2" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
@@ -6341,77 +6320,77 @@
       <c r="A4" s="15" t="s">
         <v>746</v>
       </c>
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="37" t="s">
         <v>747</v>
       </c>
-      <c r="C4" s="36"/>
+      <c r="C4" s="38"/>
       <c r="E4" s="15" t="s">
         <v>748</v>
       </c>
-      <c r="F4" s="35" t="s">
+      <c r="F4" s="37" t="s">
         <v>749</v>
       </c>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="36"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
     </row>
     <row r="5" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
         <v>750</v>
       </c>
-      <c r="B5" s="35" t="s">
+      <c r="B5" s="37" t="s">
         <v>751</v>
       </c>
-      <c r="C5" s="36"/>
+      <c r="C5" s="38"/>
       <c r="E5" s="15" t="s">
         <v>752</v>
       </c>
-      <c r="F5" s="35" t="s">
+      <c r="F5" s="37" t="s">
         <v>753</v>
       </c>
-      <c r="G5" s="36"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="36"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="38"/>
+      <c r="I5" s="38"/>
     </row>
     <row r="6" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>754</v>
       </c>
-      <c r="B6" s="35" t="s">
+      <c r="B6" s="37" t="s">
         <v>755</v>
       </c>
-      <c r="C6" s="36"/>
+      <c r="C6" s="38"/>
       <c r="E6" s="15" t="s">
         <v>756</v>
       </c>
-      <c r="F6" s="35" t="s">
+      <c r="F6" s="37" t="s">
         <v>757</v>
       </c>
-      <c r="G6" s="36"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="36"/>
+      <c r="G6" s="38"/>
+      <c r="H6" s="38"/>
+      <c r="I6" s="38"/>
     </row>
     <row r="7" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E7" s="15" t="s">
         <v>758</v>
       </c>
-      <c r="F7" s="35" t="s">
+      <c r="F7" s="37" t="s">
         <v>759</v>
       </c>
-      <c r="G7" s="36"/>
-      <c r="H7" s="36"/>
-      <c r="I7" s="36"/>
+      <c r="G7" s="38"/>
+      <c r="H7" s="38"/>
+      <c r="I7" s="38"/>
     </row>
     <row r="8" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E8" s="15" t="s">
         <v>760</v>
       </c>
-      <c r="F8" s="35" t="s">
+      <c r="F8" s="37" t="s">
         <v>761</v>
       </c>
-      <c r="G8" s="36"/>
-      <c r="H8" s="36"/>
-      <c r="I8" s="36"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="38"/>
+      <c r="I8" s="38"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="33" t="s">
@@ -6705,14 +6684,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="F3:I3"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="F4:I4"/>
-    <mergeCell ref="F7:I7"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="F5:I5"/>
     <mergeCell ref="A18:A19"/>
@@ -6728,15 +6699,23 @@
     <mergeCell ref="F6:I6"/>
     <mergeCell ref="B16:I16"/>
     <mergeCell ref="A10:I10"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="F4:I4"/>
+    <mergeCell ref="F7:I7"/>
   </mergeCells>
   <conditionalFormatting sqref="F20:F27">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
       <formula>"Pass"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>"Block"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6767,17 +6746,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="35" t="s">
         <v>183</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
     </row>
     <row r="2" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
@@ -6810,55 +6789,55 @@
       <c r="A4" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="37" t="s">
         <v>795</v>
       </c>
-      <c r="C4" s="36"/>
+      <c r="C4" s="38"/>
       <c r="E4" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="F4" s="35" t="s">
+      <c r="F4" s="37" t="s">
         <v>796</v>
       </c>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="36"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
     </row>
     <row r="5" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="B5" s="35" t="s">
+      <c r="B5" s="37" t="s">
         <v>797</v>
       </c>
-      <c r="C5" s="36"/>
+      <c r="C5" s="38"/>
       <c r="E5" s="15" t="s">
         <v>194</v>
       </c>
-      <c r="F5" s="35" t="s">
+      <c r="F5" s="37" t="s">
         <v>798</v>
       </c>
-      <c r="G5" s="36"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="36"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="38"/>
+      <c r="I5" s="38"/>
     </row>
     <row r="6" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="B6" s="35" t="s">
+      <c r="B6" s="37" t="s">
         <v>799</v>
       </c>
-      <c r="C6" s="36"/>
+      <c r="C6" s="38"/>
     </row>
     <row r="7" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
         <v>200</v>
       </c>
-      <c r="B7" s="35" t="s">
+      <c r="B7" s="37" t="s">
         <v>800</v>
       </c>
-      <c r="C7" s="36"/>
+      <c r="C7" s="38"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="33" t="s">
@@ -7152,16 +7131,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="F3:I3"/>
-    <mergeCell ref="A9:I9"/>
-    <mergeCell ref="F5:I5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B3:C3"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="F17:F18"/>
     <mergeCell ref="F4:I4"/>
@@ -7173,6 +7142,16 @@
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B15:I15"/>
     <mergeCell ref="B13:D13"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="A9:I9"/>
+    <mergeCell ref="F5:I5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B3:C3"/>
   </mergeCells>
   <conditionalFormatting sqref="F19:F26">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
@@ -8324,13 +8303,13 @@
     <mergeCell ref="B6:G6"/>
   </mergeCells>
   <conditionalFormatting sqref="G11:G28">
-    <cfRule type="cellIs" dxfId="38" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="1" operator="equal">
       <formula>"Pass"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="2" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="3" operator="equal">
       <formula>"Block"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8362,17 +8341,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="35" t="s">
         <v>183</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
     </row>
     <row r="2" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
@@ -8405,82 +8384,82 @@
       <c r="A4" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="37" t="s">
         <v>189</v>
       </c>
-      <c r="C4" s="36"/>
+      <c r="C4" s="38"/>
       <c r="E4" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="F4" s="35" t="s">
+      <c r="F4" s="37" t="s">
         <v>191</v>
       </c>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="36"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
     </row>
     <row r="5" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="B5" s="35" t="s">
+      <c r="B5" s="37" t="s">
         <v>193</v>
       </c>
-      <c r="C5" s="36"/>
+      <c r="C5" s="38"/>
       <c r="E5" s="15" t="s">
         <v>194</v>
       </c>
-      <c r="F5" s="35" t="s">
+      <c r="F5" s="37" t="s">
         <v>195</v>
       </c>
-      <c r="G5" s="36"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="36"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="38"/>
+      <c r="I5" s="38"/>
     </row>
     <row r="6" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="B6" s="35" t="s">
+      <c r="B6" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="C6" s="36"/>
+      <c r="C6" s="38"/>
       <c r="E6" s="15" t="s">
         <v>198</v>
       </c>
-      <c r="F6" s="35" t="s">
+      <c r="F6" s="37" t="s">
         <v>199</v>
       </c>
-      <c r="G6" s="36"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="36"/>
+      <c r="G6" s="38"/>
+      <c r="H6" s="38"/>
+      <c r="I6" s="38"/>
     </row>
     <row r="7" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
         <v>200</v>
       </c>
-      <c r="B7" s="35" t="s">
+      <c r="B7" s="37" t="s">
         <v>201</v>
       </c>
-      <c r="C7" s="36"/>
+      <c r="C7" s="38"/>
     </row>
     <row r="8" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
         <v>202</v>
       </c>
-      <c r="B8" s="35" t="s">
+      <c r="B8" s="37" t="s">
         <v>203</v>
       </c>
-      <c r="C8" s="36"/>
+      <c r="C8" s="38"/>
     </row>
     <row r="9" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
         <v>204</v>
       </c>
-      <c r="B9" s="35" t="s">
+      <c r="B9" s="37" t="s">
         <v>205</v>
       </c>
-      <c r="C9" s="36"/>
+      <c r="C9" s="38"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="33" t="s">
@@ -8894,6 +8873,14 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="B17:I17"/>
+    <mergeCell ref="F4:I4"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="F6:I6"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="E2:F2"/>
@@ -8910,23 +8897,15 @@
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B16:I16"/>
-    <mergeCell ref="E19:E20"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="F19:F20"/>
-    <mergeCell ref="B17:I17"/>
-    <mergeCell ref="F4:I4"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="F6:I6"/>
   </mergeCells>
   <conditionalFormatting sqref="F21:F34">
-    <cfRule type="cellIs" dxfId="35" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="1" operator="equal">
       <formula>"Pass"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="2" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="3" operator="equal">
       <formula>"Block"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8958,17 +8937,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="35" t="s">
         <v>183</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
     </row>
     <row r="2" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
@@ -9001,117 +8980,117 @@
       <c r="A4" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="37" t="s">
         <v>262</v>
       </c>
-      <c r="C4" s="36"/>
+      <c r="C4" s="38"/>
       <c r="E4" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="F4" s="35" t="s">
+      <c r="F4" s="37" t="s">
         <v>263</v>
       </c>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="36"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
     </row>
     <row r="5" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="B5" s="35" t="s">
+      <c r="B5" s="37" t="s">
         <v>264</v>
       </c>
-      <c r="C5" s="36"/>
+      <c r="C5" s="38"/>
       <c r="E5" s="15" t="s">
         <v>194</v>
       </c>
-      <c r="F5" s="35" t="s">
+      <c r="F5" s="37" t="s">
         <v>265</v>
       </c>
-      <c r="G5" s="36"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="36"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="38"/>
+      <c r="I5" s="38"/>
     </row>
     <row r="6" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="B6" s="35" t="s">
+      <c r="B6" s="37" t="s">
         <v>266</v>
       </c>
-      <c r="C6" s="36"/>
+      <c r="C6" s="38"/>
       <c r="E6" s="15" t="s">
         <v>198</v>
       </c>
-      <c r="F6" s="35" t="s">
+      <c r="F6" s="37" t="s">
         <v>267</v>
       </c>
-      <c r="G6" s="36"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="36"/>
+      <c r="G6" s="38"/>
+      <c r="H6" s="38"/>
+      <c r="I6" s="38"/>
     </row>
     <row r="7" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
         <v>200</v>
       </c>
-      <c r="B7" s="35" t="s">
+      <c r="B7" s="37" t="s">
         <v>268</v>
       </c>
-      <c r="C7" s="36"/>
+      <c r="C7" s="38"/>
       <c r="E7" s="15" t="s">
         <v>269</v>
       </c>
-      <c r="F7" s="35" t="s">
+      <c r="F7" s="37" t="s">
         <v>270</v>
       </c>
-      <c r="G7" s="36"/>
-      <c r="H7" s="36"/>
-      <c r="I7" s="36"/>
+      <c r="G7" s="38"/>
+      <c r="H7" s="38"/>
+      <c r="I7" s="38"/>
     </row>
     <row r="8" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E8" s="15" t="s">
         <v>271</v>
       </c>
-      <c r="F8" s="35" t="s">
+      <c r="F8" s="37" t="s">
         <v>272</v>
       </c>
-      <c r="G8" s="36"/>
-      <c r="H8" s="36"/>
-      <c r="I8" s="36"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="38"/>
+      <c r="I8" s="38"/>
     </row>
     <row r="9" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E9" s="15" t="s">
         <v>273</v>
       </c>
-      <c r="F9" s="35" t="s">
+      <c r="F9" s="37" t="s">
         <v>274</v>
       </c>
-      <c r="G9" s="36"/>
-      <c r="H9" s="36"/>
-      <c r="I9" s="36"/>
+      <c r="G9" s="38"/>
+      <c r="H9" s="38"/>
+      <c r="I9" s="38"/>
     </row>
     <row r="10" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E10" s="15" t="s">
         <v>275</v>
       </c>
-      <c r="F10" s="35" t="s">
+      <c r="F10" s="37" t="s">
         <v>276</v>
       </c>
-      <c r="G10" s="36"/>
-      <c r="H10" s="36"/>
-      <c r="I10" s="36"/>
+      <c r="G10" s="38"/>
+      <c r="H10" s="38"/>
+      <c r="I10" s="38"/>
     </row>
     <row r="11" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E11" s="15" t="s">
         <v>277</v>
       </c>
-      <c r="F11" s="35" t="s">
+      <c r="F11" s="37" t="s">
         <v>278</v>
       </c>
-      <c r="G11" s="36"/>
-      <c r="H11" s="36"/>
-      <c r="I11" s="36"/>
+      <c r="G11" s="38"/>
+      <c r="H11" s="38"/>
+      <c r="I11" s="38"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="33" t="s">
@@ -9485,6 +9464,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="F9:I9"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B18:I18"/>
+    <mergeCell ref="F4:I4"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="F11:I11"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="F10:I10"/>
+    <mergeCell ref="F6:I6"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="D21:D22"/>
@@ -9501,26 +9491,15 @@
     <mergeCell ref="B19:I19"/>
     <mergeCell ref="E21:E22"/>
     <mergeCell ref="B7:C7"/>
-    <mergeCell ref="F9:I9"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B18:I18"/>
-    <mergeCell ref="F4:I4"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="F11:I11"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="F10:I10"/>
-    <mergeCell ref="F6:I6"/>
   </mergeCells>
   <conditionalFormatting sqref="F23:F34">
-    <cfRule type="cellIs" dxfId="32" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="1" operator="equal">
       <formula>"Pass"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="2" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="3" operator="equal">
       <formula>"Block"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11108,13 +11087,13 @@
     <mergeCell ref="B21:E21"/>
   </mergeCells>
   <conditionalFormatting sqref="G27:G76">
-    <cfRule type="cellIs" dxfId="29" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="1" operator="equal">
       <formula>"Pass"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="2" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="3" operator="equal">
       <formula>"Block"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11145,17 +11124,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="35" t="s">
         <v>183</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
     </row>
     <row r="2" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
@@ -11188,107 +11167,107 @@
       <c r="A4" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="37" t="s">
         <v>425</v>
       </c>
-      <c r="C4" s="36"/>
+      <c r="C4" s="38"/>
       <c r="E4" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="F4" s="35" t="s">
+      <c r="F4" s="37" t="s">
         <v>426</v>
       </c>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="36"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
     </row>
     <row r="5" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E5" s="15" t="s">
         <v>194</v>
       </c>
-      <c r="F5" s="35" t="s">
+      <c r="F5" s="37" t="s">
         <v>427</v>
       </c>
-      <c r="G5" s="36"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="36"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="38"/>
+      <c r="I5" s="38"/>
     </row>
     <row r="6" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E6" s="15" t="s">
         <v>198</v>
       </c>
-      <c r="F6" s="35" t="s">
+      <c r="F6" s="37" t="s">
         <v>428</v>
       </c>
-      <c r="G6" s="36"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="36"/>
+      <c r="G6" s="38"/>
+      <c r="H6" s="38"/>
+      <c r="I6" s="38"/>
     </row>
     <row r="7" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E7" s="15" t="s">
         <v>269</v>
       </c>
-      <c r="F7" s="35" t="s">
+      <c r="F7" s="37" t="s">
         <v>429</v>
       </c>
-      <c r="G7" s="36"/>
-      <c r="H7" s="36"/>
-      <c r="I7" s="36"/>
+      <c r="G7" s="38"/>
+      <c r="H7" s="38"/>
+      <c r="I7" s="38"/>
     </row>
     <row r="8" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E8" s="15" t="s">
         <v>271</v>
       </c>
-      <c r="F8" s="35" t="s">
+      <c r="F8" s="37" t="s">
         <v>430</v>
       </c>
-      <c r="G8" s="36"/>
-      <c r="H8" s="36"/>
-      <c r="I8" s="36"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="38"/>
+      <c r="I8" s="38"/>
     </row>
     <row r="9" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E9" s="15" t="s">
         <v>273</v>
       </c>
-      <c r="F9" s="35" t="s">
+      <c r="F9" s="37" t="s">
         <v>431</v>
       </c>
-      <c r="G9" s="36"/>
-      <c r="H9" s="36"/>
-      <c r="I9" s="36"/>
+      <c r="G9" s="38"/>
+      <c r="H9" s="38"/>
+      <c r="I9" s="38"/>
     </row>
     <row r="10" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E10" s="15" t="s">
         <v>275</v>
       </c>
-      <c r="F10" s="35" t="s">
+      <c r="F10" s="37" t="s">
         <v>432</v>
       </c>
-      <c r="G10" s="36"/>
-      <c r="H10" s="36"/>
-      <c r="I10" s="36"/>
+      <c r="G10" s="38"/>
+      <c r="H10" s="38"/>
+      <c r="I10" s="38"/>
     </row>
     <row r="11" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E11" s="15" t="s">
         <v>277</v>
       </c>
-      <c r="F11" s="35" t="s">
+      <c r="F11" s="37" t="s">
         <v>433</v>
       </c>
-      <c r="G11" s="36"/>
-      <c r="H11" s="36"/>
-      <c r="I11" s="36"/>
+      <c r="G11" s="38"/>
+      <c r="H11" s="38"/>
+      <c r="I11" s="38"/>
     </row>
     <row r="12" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E12" s="15" t="s">
         <v>434</v>
       </c>
-      <c r="F12" s="35" t="s">
+      <c r="F12" s="37" t="s">
         <v>435</v>
       </c>
-      <c r="G12" s="36"/>
-      <c r="H12" s="36"/>
-      <c r="I12" s="36"/>
+      <c r="G12" s="38"/>
+      <c r="H12" s="38"/>
+      <c r="I12" s="38"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="33" t="s">
@@ -11622,6 +11601,15 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="B20:I20"/>
+    <mergeCell ref="F4:I4"/>
+    <mergeCell ref="A14:I14"/>
+    <mergeCell ref="F11:I11"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="F10:I10"/>
+    <mergeCell ref="F6:I6"/>
+    <mergeCell ref="F7:I7"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="D22:D23"/>
@@ -11638,24 +11626,15 @@
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="E22:E23"/>
-    <mergeCell ref="B20:I20"/>
-    <mergeCell ref="F4:I4"/>
-    <mergeCell ref="A14:I14"/>
-    <mergeCell ref="F11:I11"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="F10:I10"/>
-    <mergeCell ref="F6:I6"/>
-    <mergeCell ref="F7:I7"/>
   </mergeCells>
   <conditionalFormatting sqref="F24:F33">
-    <cfRule type="cellIs" dxfId="26" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="1" operator="equal">
       <formula>"Pass"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="2" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="3" operator="equal">
       <formula>"Block"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12396,13 +12375,13 @@
     <mergeCell ref="F23:F24"/>
   </mergeCells>
   <conditionalFormatting sqref="G25:G39">
-    <cfRule type="cellIs" dxfId="23" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
       <formula>"Pass"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="2" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="3" operator="equal">
       <formula>"Block"</formula>
     </cfRule>
   </conditionalFormatting>
